--- a/scenarios/Coal_Flexibilisation/sub_scenarios/operational_constraints.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/operational_constraints.xlsx
@@ -699,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -2346,6 +2346,502 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>NO_GAS_FLOOR</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="15">
+        <v>1</v>
+      </c>
+      <c r="K13" s="15">
+        <v>1</v>
+      </c>
+      <c r="L13" s="15">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <v>1</v>
+      </c>
+      <c r="N13" s="15">
+        <v>1</v>
+      </c>
+      <c r="O13" s="14">
+        <v>1</v>
+      </c>
+      <c r="P13" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>1</v>
+      </c>
+      <c r="R13" s="15">
+        <v>1</v>
+      </c>
+      <c r="S13" s="15">
+        <v>1</v>
+      </c>
+      <c r="T13" s="14">
+        <v>1</v>
+      </c>
+      <c r="U13" s="15">
+        <v>1</v>
+      </c>
+      <c r="V13" s="15">
+        <v>1</v>
+      </c>
+      <c r="W13" s="15">
+        <v>1</v>
+      </c>
+      <c r="X13" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="14">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AK13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>NO_GAS_FLOOR</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="L14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="O14" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="P14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="R14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="S14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="X14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AA14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AB14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="AE14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AF14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AG14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AH14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AI14" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="AJ14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AK14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AL14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AM14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AN14" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>NO_GAS_FLOOR</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="K15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="L15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="M15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="N15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="O15" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="P15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="Q15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="R15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="S15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="T15" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="U15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="V15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="W15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="X15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="Y15" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="Z15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="AA15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="AB15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="AC15" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="AD15" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="16">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>NO_GAS_FLOOR</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="K16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="L16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="M16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="N16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="O16" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="P16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="Q16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="R16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="S16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="T16" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="U16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="V16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="W16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="X16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="Y16" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="Z16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AB16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AC16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AD16" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="AE16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AF16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AG16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AH16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AI16" s="33">
+        <v>2.8</v>
+      </c>
+      <c r="AJ16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AK16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AL16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AM16" s="32">
+        <v>2.8</v>
+      </c>
+      <c r="AN16" s="34">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A2:A12">
